--- a/MidiPyGenStatus.xlsx
+++ b/MidiPyGenStatus.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="78">
   <si>
     <t>Date</t>
   </si>
@@ -136,13 +136,130 @@
   </si>
   <si>
     <t>MidiBot Version 0.6?????</t>
+  </si>
+  <si>
+    <t>1) Added instUse bool to complement the chordUse bool</t>
+  </si>
+  <si>
+    <t>2) Fixed optimum diatonic to include nearest diatonic up or down</t>
+  </si>
+  <si>
+    <t>1) Same instrument can be most optimum for 2 diatonics</t>
+  </si>
+  <si>
+    <t>1) Run Canon in D</t>
+  </si>
+  <si>
+    <t>2) The last dominant chord, flute appears twice as optimum</t>
+  </si>
+  <si>
+    <t>3) Flute optimum is for both 7 and 2</t>
+  </si>
+  <si>
+    <t>4) Clarinet optimum would be only for 7</t>
+  </si>
+  <si>
+    <t>5) Because 7 occurs first in the diatonic loop, flute will pick 7</t>
+  </si>
+  <si>
+    <t>Previous(Fl:1,Cl:6) Chosen(Fl:7,Cl:2) Desired(Fl:2,Cl:7)</t>
+  </si>
+  <si>
+    <t>6) That leaves clarinet to jump all the way to 2</t>
+  </si>
+  <si>
+    <t>Replicate</t>
+  </si>
+  <si>
+    <t>Fix in work</t>
+  </si>
+  <si>
+    <t>1) When instrument is double optimum, array of [0,0,1] will form</t>
+  </si>
+  <si>
+    <t>I.E.</t>
+  </si>
+  <si>
+    <t>Chord: IV to I</t>
+  </si>
+  <si>
+    <t>Chord 1 Opt (3: Tr, 5: Tr)</t>
+  </si>
+  <si>
+    <t>First: Tr: 4, Cl: 6</t>
+  </si>
+  <si>
+    <t>Desired Second: Tr: 3, Cl: 5</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Test jumps for all instruments that are not bass</t>
+  </si>
+  <si>
+    <t>Flute (1)</t>
+  </si>
+  <si>
+    <t>Clarinet (6)</t>
+  </si>
+  <si>
+    <t>Trumpet (4)</t>
+  </si>
+  <si>
+    <t>dEnd1 (3)</t>
+  </si>
+  <si>
+    <t>dEnd2 (5)</t>
+  </si>
+  <si>
+    <t>Flute(1)</t>
+  </si>
+  <si>
+    <t>dEnd2 (2)</t>
+  </si>
+  <si>
+    <t>dEnd1 (7)</t>
+  </si>
+  <si>
+    <t>Trumpet(4)</t>
+  </si>
+  <si>
+    <t>Clarinet(6)</t>
+  </si>
+  <si>
+    <t>Restructuring of code to use a genetic algorithm to solve for optimum parts generation (after first chord)</t>
+  </si>
+  <si>
+    <t>Effectively minimizes jumps and deviations from first note</t>
+  </si>
+  <si>
+    <t>To Do</t>
+  </si>
+  <si>
+    <t>Create a chord progression generator instead of hard coding diatonic values</t>
+  </si>
+  <si>
+    <t>Add Melodies</t>
+  </si>
+  <si>
+    <t>Much higher success rate</t>
+  </si>
+  <si>
+    <t>Also try to see if you can use passing tones</t>
+  </si>
+  <si>
+    <t>Auto generate unique rhythms instead of straight up using long tones</t>
+  </si>
+  <si>
+    <t>Add Percussion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,6 +279,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -448,7 +572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -528,6 +652,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -809,20 +935,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J150"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.3671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.3671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.83984375" style="2"/>
-    <col min="4" max="4" width="17.9453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.41796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7890625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.83984375" style="1"/>
-    <col min="8" max="8" width="17.9453125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.68359375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="4" max="4" width="18" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="18" style="1" customWidth="1"/>
+    <col min="9" max="9" width="30.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -844,7 +970,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="17">
         <v>43083</v>
       </c>
@@ -863,7 +989,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="17">
         <v>43083</v>
       </c>
@@ -882,7 +1008,7 @@
       <c r="H3" s="20"/>
       <c r="I3" s="21"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="45">
         <v>43095</v>
       </c>
@@ -901,7 +1027,7 @@
       <c r="H4" s="24"/>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="45"/>
       <c r="B5" s="41"/>
       <c r="C5" s="46"/>
@@ -916,7 +1042,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="27"/>
     </row>
-    <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="45"/>
       <c r="B6" s="41"/>
       <c r="C6" s="46"/>
@@ -931,7 +1057,7 @@
       <c r="H6" s="8"/>
       <c r="I6" s="27"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="45"/>
       <c r="B7" s="41"/>
       <c r="C7" s="46"/>
@@ -946,7 +1072,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="27"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="45"/>
       <c r="B8" s="41"/>
       <c r="C8" s="46"/>
@@ -961,7 +1087,7 @@
       <c r="H8" s="8"/>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="45"/>
       <c r="B9" s="41"/>
       <c r="C9" s="46"/>
@@ -974,7 +1100,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="27"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="45"/>
       <c r="B10" s="41"/>
       <c r="C10" s="46"/>
@@ -987,7 +1113,7 @@
       <c r="H10" s="8"/>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="45"/>
       <c r="B11" s="42"/>
       <c r="C11" s="46"/>
@@ -1000,7 +1126,7 @@
       <c r="H11" s="30"/>
       <c r="I11" s="31"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="34">
         <v>43097</v>
       </c>
@@ -1019,7 +1145,7 @@
       <c r="H12" s="24"/>
       <c r="I12" s="25"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="35"/>
       <c r="B13" s="41"/>
       <c r="C13" s="38"/>
@@ -1034,7 +1160,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="27"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="35"/>
       <c r="B14" s="41"/>
       <c r="C14" s="38"/>
@@ -1049,7 +1175,7 @@
       <c r="H14" s="8"/>
       <c r="I14" s="27"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="35"/>
       <c r="B15" s="41"/>
       <c r="C15" s="38"/>
@@ -1064,7 +1190,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="27"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="35"/>
       <c r="B16" s="41"/>
       <c r="C16" s="38"/>
@@ -1077,7 +1203,7 @@
       <c r="H16" s="8"/>
       <c r="I16" s="27"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="35"/>
       <c r="B17" s="41"/>
       <c r="C17" s="38"/>
@@ -1090,7 +1216,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="27"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="35"/>
       <c r="B18" s="41"/>
       <c r="C18" s="38"/>
@@ -1103,7 +1229,7 @@
       <c r="H18" s="8"/>
       <c r="I18" s="27"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="35"/>
       <c r="B19" s="41"/>
       <c r="C19" s="38"/>
@@ -1114,7 +1240,7 @@
       <c r="H19" s="8"/>
       <c r="I19" s="27"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="35"/>
       <c r="B20" s="41"/>
       <c r="C20" s="38"/>
@@ -1129,7 +1255,7 @@
       <c r="H20" s="8"/>
       <c r="I20" s="27"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="35"/>
       <c r="B21" s="41"/>
       <c r="C21" s="38"/>
@@ -1144,7 +1270,7 @@
       <c r="H21" s="8"/>
       <c r="I21" s="27"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="35"/>
       <c r="B22" s="41"/>
       <c r="C22" s="38"/>
@@ -1159,7 +1285,7 @@
       <c r="H22" s="8"/>
       <c r="I22" s="27"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="35"/>
       <c r="B23" s="41"/>
       <c r="C23" s="38"/>
@@ -1174,7 +1300,7 @@
       <c r="H23" s="8"/>
       <c r="I23" s="27"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="36"/>
       <c r="B24" s="42"/>
       <c r="C24" s="39"/>
@@ -1189,315 +1315,454 @@
       <c r="H24" s="30"/>
       <c r="I24" s="31"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="9"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="45">
+        <v>43100</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="25"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="45"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="26" t="s">
+        <v>22</v>
+      </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="G26" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="H26" s="8"/>
-      <c r="I26" s="9"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
+      <c r="I26" s="27"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="45"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="28" t="s">
+        <v>39</v>
+      </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="G27" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="H27" s="8"/>
-      <c r="I27" s="9"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="32"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
+      <c r="I27" s="27"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="45"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="G28" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="H28" s="8"/>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
+      <c r="I28" s="27"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="45"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="26" t="s">
+        <v>50</v>
+      </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="G29" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="H29" s="8"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="I29" s="27"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="45"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="28" t="s">
+        <v>51</v>
+      </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="G30" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="H30" s="8"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
+      <c r="I30" s="27"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="45"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="28" t="s">
+        <v>52</v>
+      </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="G31" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="H31" s="8"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
+      <c r="I31" s="27"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="45"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="G32" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="H32" s="8"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
+      <c r="I32" s="27"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="45"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="28" t="s">
+        <v>55</v>
+      </c>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="G33" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="H33" s="8"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="I33" s="27"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="45"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="28" t="s">
+        <v>56</v>
+      </c>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="G34" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="H34" s="8"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="32"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
+      <c r="I34" s="27"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="45"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="28" t="s">
+        <v>58</v>
+      </c>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="G35" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="H35" s="8"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="I35" s="27"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G36" s="12"/>
       <c r="H36" s="8"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="I36" s="27"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="45"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" s="8">
+        <f>3-1</f>
+        <v>2</v>
+      </c>
+      <c r="F37" s="8">
+        <f>5-1</f>
+        <v>4</v>
+      </c>
+      <c r="G37" s="8">
+        <f>ABS(E37)+ABS(F37)</f>
+        <v>6</v>
+      </c>
       <c r="H37" s="8"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="32"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="I37" s="27"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="45"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="8">
+        <f>3-6</f>
+        <v>-3</v>
+      </c>
+      <c r="F38" s="8">
+        <f>5-6</f>
+        <v>-1</v>
+      </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="32"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="I38" s="27"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="45"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" s="8">
+        <f>3-4</f>
+        <v>-1</v>
+      </c>
+      <c r="F39" s="8">
+        <f>5-4</f>
+        <v>1</v>
+      </c>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="32"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
+      <c r="I39" s="27"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="45"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="32"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
+      <c r="I40" s="27"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="45"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="8">
+        <f>7-1-7</f>
+        <v>-1</v>
+      </c>
+      <c r="F41" s="8">
+        <f>2-1</f>
+        <v>1</v>
+      </c>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="32"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
+      <c r="I41" s="27"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="45"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="8">
+        <f>6-7</f>
+        <v>-1</v>
+      </c>
+      <c r="F42" s="8">
+        <f>6-2</f>
+        <v>4</v>
+      </c>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
-      <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="32"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="32"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="9"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="32"/>
-      <c r="B45" s="32"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
+      <c r="I42" s="27"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="45"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="30">
+        <f>7-4</f>
+        <v>3</v>
+      </c>
+      <c r="F43" s="30">
+        <f>2-4</f>
+        <v>-2</v>
+      </c>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="31"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="40">
+        <v>43104</v>
+      </c>
+      <c r="B44" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="25"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="41"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="28" t="s">
+        <v>69</v>
+      </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
-      <c r="I45" s="9"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="32"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+      <c r="I45" s="27"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="41"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="28" t="s">
+        <v>70</v>
+      </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
-      <c r="I46" s="9"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="32"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
+      <c r="I46" s="27"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="41"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="26" t="s">
+        <v>71</v>
+      </c>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
-      <c r="I47" s="9"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="32"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
+      <c r="I47" s="27"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="41"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="28" t="s">
+        <v>72</v>
+      </c>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
-      <c r="I48" s="9"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="32"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
+      <c r="I48" s="27"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="41"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="28" t="s">
+        <v>76</v>
+      </c>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
-      <c r="I49" s="9"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="32"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
+      <c r="I49" s="27"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="41"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
-      <c r="I50" s="9"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="32"/>
-      <c r="B51" s="32"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
+      <c r="I50" s="27"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="41"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="28" t="s">
+        <v>73</v>
+      </c>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
-      <c r="I51" s="9"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="32"/>
-      <c r="B52" s="32"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="9"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="I51" s="27"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="42"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="31"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="32"/>
       <c r="B53" s="32"/>
       <c r="C53" s="7"/>
@@ -1508,7 +1773,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="32"/>
       <c r="B54" s="32"/>
       <c r="C54" s="7"/>
@@ -1519,7 +1784,7 @@
       <c r="H54" s="8"/>
       <c r="I54" s="9"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="32"/>
       <c r="B55" s="32"/>
       <c r="C55" s="7"/>
@@ -1530,7 +1795,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="32"/>
       <c r="B56" s="32"/>
       <c r="C56" s="7"/>
@@ -1541,7 +1806,7 @@
       <c r="H56" s="8"/>
       <c r="I56" s="9"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="32"/>
       <c r="B57" s="32"/>
       <c r="C57" s="7"/>
@@ -1552,7 +1817,7 @@
       <c r="H57" s="8"/>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="32"/>
       <c r="B58" s="32"/>
       <c r="C58" s="7"/>
@@ -1563,7 +1828,7 @@
       <c r="H58" s="8"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="32"/>
       <c r="B59" s="32"/>
       <c r="C59" s="7"/>
@@ -1574,7 +1839,7 @@
       <c r="H59" s="8"/>
       <c r="I59" s="9"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="32"/>
       <c r="B60" s="32"/>
       <c r="C60" s="7"/>
@@ -1585,7 +1850,7 @@
       <c r="H60" s="8"/>
       <c r="I60" s="9"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="32"/>
       <c r="B61" s="32"/>
       <c r="C61" s="7"/>
@@ -1596,7 +1861,7 @@
       <c r="H61" s="8"/>
       <c r="I61" s="9"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="32"/>
       <c r="B62" s="32"/>
       <c r="C62" s="7"/>
@@ -1607,7 +1872,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="9"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="32"/>
       <c r="B63" s="32"/>
       <c r="C63" s="7"/>
@@ -1618,7 +1883,7 @@
       <c r="H63" s="8"/>
       <c r="I63" s="9"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="32"/>
       <c r="B64" s="32"/>
       <c r="C64" s="7"/>
@@ -1629,7 +1894,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="9"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="32"/>
       <c r="B65" s="32"/>
       <c r="C65" s="7"/>
@@ -1640,7 +1905,7 @@
       <c r="H65" s="8"/>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="32"/>
       <c r="B66" s="32"/>
       <c r="C66" s="7"/>
@@ -1651,7 +1916,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="32"/>
       <c r="B67" s="32"/>
       <c r="C67" s="7"/>
@@ -1662,7 +1927,7 @@
       <c r="H67" s="8"/>
       <c r="I67" s="9"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="32"/>
       <c r="B68" s="32"/>
       <c r="C68" s="7"/>
@@ -1673,7 +1938,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="9"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="32"/>
       <c r="B69" s="32"/>
       <c r="C69" s="7"/>
@@ -1684,7 +1949,7 @@
       <c r="H69" s="8"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="32"/>
       <c r="B70" s="32"/>
       <c r="C70" s="7"/>
@@ -1695,7 +1960,7 @@
       <c r="H70" s="8"/>
       <c r="I70" s="9"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="32"/>
       <c r="B71" s="32"/>
       <c r="C71" s="7"/>
@@ -1706,7 +1971,7 @@
       <c r="H71" s="8"/>
       <c r="I71" s="9"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="32"/>
       <c r="B72" s="32"/>
       <c r="C72" s="7"/>
@@ -1717,7 +1982,7 @@
       <c r="H72" s="8"/>
       <c r="I72" s="9"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="32"/>
       <c r="B73" s="32"/>
       <c r="C73" s="7"/>
@@ -1728,7 +1993,7 @@
       <c r="H73" s="8"/>
       <c r="I73" s="9"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="32"/>
       <c r="B74" s="32"/>
       <c r="C74" s="7"/>
@@ -1739,7 +2004,7 @@
       <c r="H74" s="8"/>
       <c r="I74" s="9"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="32"/>
       <c r="B75" s="32"/>
       <c r="C75" s="7"/>
@@ -1750,7 +2015,7 @@
       <c r="H75" s="8"/>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="32"/>
       <c r="B76" s="32"/>
       <c r="C76" s="7"/>
@@ -1761,7 +2026,7 @@
       <c r="H76" s="8"/>
       <c r="I76" s="9"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="32"/>
       <c r="B77" s="32"/>
       <c r="C77" s="7"/>
@@ -1772,7 +2037,7 @@
       <c r="H77" s="8"/>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="32"/>
       <c r="B78" s="32"/>
       <c r="C78" s="7"/>
@@ -1783,7 +2048,7 @@
       <c r="H78" s="8"/>
       <c r="I78" s="9"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="32"/>
       <c r="B79" s="32"/>
       <c r="C79" s="7"/>
@@ -1794,7 +2059,7 @@
       <c r="H79" s="8"/>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="32"/>
       <c r="B80" s="32"/>
       <c r="C80" s="7"/>
@@ -1805,7 +2070,7 @@
       <c r="H80" s="8"/>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="32"/>
       <c r="B81" s="32"/>
       <c r="C81" s="7"/>
@@ -1816,7 +2081,7 @@
       <c r="H81" s="8"/>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="32"/>
       <c r="B82" s="32"/>
       <c r="C82" s="7"/>
@@ -1827,7 +2092,7 @@
       <c r="H82" s="8"/>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="32"/>
       <c r="B83" s="32"/>
       <c r="C83" s="7"/>
@@ -1838,7 +2103,7 @@
       <c r="H83" s="8"/>
       <c r="I83" s="9"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="32"/>
       <c r="B84" s="32"/>
       <c r="C84" s="7"/>
@@ -1849,7 +2114,7 @@
       <c r="H84" s="8"/>
       <c r="I84" s="9"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="32"/>
       <c r="B85" s="32"/>
       <c r="C85" s="7"/>
@@ -1860,7 +2125,7 @@
       <c r="H85" s="8"/>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="32"/>
       <c r="B86" s="32"/>
       <c r="C86" s="7"/>
@@ -1871,7 +2136,7 @@
       <c r="H86" s="8"/>
       <c r="I86" s="9"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="32"/>
       <c r="B87" s="32"/>
       <c r="C87" s="7"/>
@@ -1882,7 +2147,7 @@
       <c r="H87" s="8"/>
       <c r="I87" s="9"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="32"/>
       <c r="B88" s="32"/>
       <c r="C88" s="7"/>
@@ -1893,7 +2158,7 @@
       <c r="H88" s="8"/>
       <c r="I88" s="9"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="32"/>
       <c r="B89" s="32"/>
       <c r="C89" s="7"/>
@@ -1904,7 +2169,7 @@
       <c r="H89" s="8"/>
       <c r="I89" s="9"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="32"/>
       <c r="B90" s="32"/>
       <c r="C90" s="7"/>
@@ -1915,7 +2180,7 @@
       <c r="H90" s="8"/>
       <c r="I90" s="9"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="32"/>
       <c r="B91" s="32"/>
       <c r="C91" s="7"/>
@@ -1926,7 +2191,7 @@
       <c r="H91" s="8"/>
       <c r="I91" s="9"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="32"/>
       <c r="B92" s="32"/>
       <c r="C92" s="7"/>
@@ -1937,7 +2202,7 @@
       <c r="H92" s="8"/>
       <c r="I92" s="9"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="32"/>
       <c r="B93" s="32"/>
       <c r="C93" s="7"/>
@@ -1948,7 +2213,7 @@
       <c r="H93" s="8"/>
       <c r="I93" s="9"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="32"/>
       <c r="B94" s="32"/>
       <c r="C94" s="7"/>
@@ -1959,7 +2224,7 @@
       <c r="H94" s="8"/>
       <c r="I94" s="9"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="32"/>
       <c r="B95" s="32"/>
       <c r="C95" s="7"/>
@@ -1970,7 +2235,7 @@
       <c r="H95" s="8"/>
       <c r="I95" s="9"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="32"/>
       <c r="B96" s="32"/>
       <c r="C96" s="7"/>
@@ -1981,7 +2246,7 @@
       <c r="H96" s="8"/>
       <c r="I96" s="9"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="32"/>
       <c r="B97" s="32"/>
       <c r="C97" s="7"/>
@@ -1992,7 +2257,7 @@
       <c r="H97" s="8"/>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="32"/>
       <c r="B98" s="32"/>
       <c r="C98" s="7"/>
@@ -2003,7 +2268,7 @@
       <c r="H98" s="8"/>
       <c r="I98" s="9"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="32"/>
       <c r="B99" s="32"/>
       <c r="C99" s="7"/>
@@ -2014,7 +2279,7 @@
       <c r="H99" s="8"/>
       <c r="I99" s="9"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="32"/>
       <c r="B100" s="32"/>
       <c r="C100" s="7"/>
@@ -2025,7 +2290,7 @@
       <c r="H100" s="8"/>
       <c r="I100" s="9"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="32"/>
       <c r="B101" s="32"/>
       <c r="C101" s="7"/>
@@ -2036,7 +2301,7 @@
       <c r="H101" s="8"/>
       <c r="I101" s="9"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="32"/>
       <c r="B102" s="32"/>
       <c r="C102" s="7"/>
@@ -2047,7 +2312,7 @@
       <c r="H102" s="8"/>
       <c r="I102" s="9"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="32"/>
       <c r="B103" s="32"/>
       <c r="C103" s="7"/>
@@ -2058,7 +2323,7 @@
       <c r="H103" s="8"/>
       <c r="I103" s="9"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="32"/>
       <c r="B104" s="32"/>
       <c r="C104" s="7"/>
@@ -2069,7 +2334,7 @@
       <c r="H104" s="8"/>
       <c r="I104" s="9"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="32"/>
       <c r="B105" s="32"/>
       <c r="C105" s="7"/>
@@ -2080,7 +2345,7 @@
       <c r="H105" s="8"/>
       <c r="I105" s="9"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="32"/>
       <c r="B106" s="32"/>
       <c r="C106" s="7"/>
@@ -2091,7 +2356,7 @@
       <c r="H106" s="8"/>
       <c r="I106" s="9"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="32"/>
       <c r="B107" s="32"/>
       <c r="C107" s="7"/>
@@ -2102,7 +2367,7 @@
       <c r="H107" s="8"/>
       <c r="I107" s="9"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="32"/>
       <c r="B108" s="32"/>
       <c r="C108" s="7"/>
@@ -2113,7 +2378,7 @@
       <c r="H108" s="8"/>
       <c r="I108" s="9"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="32"/>
       <c r="B109" s="32"/>
       <c r="C109" s="7"/>
@@ -2124,7 +2389,7 @@
       <c r="H109" s="8"/>
       <c r="I109" s="9"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="32"/>
       <c r="B110" s="32"/>
       <c r="C110" s="7"/>
@@ -2135,7 +2400,7 @@
       <c r="H110" s="8"/>
       <c r="I110" s="9"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="32"/>
       <c r="B111" s="32"/>
       <c r="C111" s="7"/>
@@ -2146,7 +2411,7 @@
       <c r="H111" s="8"/>
       <c r="I111" s="9"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="32"/>
       <c r="B112" s="32"/>
       <c r="C112" s="7"/>
@@ -2157,7 +2422,7 @@
       <c r="H112" s="8"/>
       <c r="I112" s="9"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="32"/>
       <c r="B113" s="32"/>
       <c r="C113" s="7"/>
@@ -2168,7 +2433,7 @@
       <c r="H113" s="8"/>
       <c r="I113" s="9"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="32"/>
       <c r="B114" s="32"/>
       <c r="C114" s="7"/>
@@ -2179,7 +2444,7 @@
       <c r="H114" s="8"/>
       <c r="I114" s="9"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="32"/>
       <c r="B115" s="32"/>
       <c r="C115" s="7"/>
@@ -2190,7 +2455,7 @@
       <c r="H115" s="8"/>
       <c r="I115" s="9"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="32"/>
       <c r="B116" s="32"/>
       <c r="C116" s="7"/>
@@ -2201,7 +2466,7 @@
       <c r="H116" s="8"/>
       <c r="I116" s="9"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="32"/>
       <c r="B117" s="32"/>
       <c r="C117" s="7"/>
@@ -2212,7 +2477,7 @@
       <c r="H117" s="8"/>
       <c r="I117" s="9"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="32"/>
       <c r="B118" s="32"/>
       <c r="C118" s="7"/>
@@ -2223,7 +2488,7 @@
       <c r="H118" s="8"/>
       <c r="I118" s="9"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="32"/>
       <c r="B119" s="32"/>
       <c r="C119" s="7"/>
@@ -2234,7 +2499,7 @@
       <c r="H119" s="8"/>
       <c r="I119" s="9"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="32"/>
       <c r="B120" s="32"/>
       <c r="C120" s="7"/>
@@ -2245,7 +2510,7 @@
       <c r="H120" s="8"/>
       <c r="I120" s="9"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="32"/>
       <c r="B121" s="32"/>
       <c r="C121" s="7"/>
@@ -2256,7 +2521,7 @@
       <c r="H121" s="8"/>
       <c r="I121" s="9"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="32"/>
       <c r="B122" s="32"/>
       <c r="C122" s="7"/>
@@ -2267,7 +2532,7 @@
       <c r="H122" s="8"/>
       <c r="I122" s="9"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="32"/>
       <c r="B123" s="32"/>
       <c r="C123" s="7"/>
@@ -2278,7 +2543,7 @@
       <c r="H123" s="8"/>
       <c r="I123" s="9"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="32"/>
       <c r="B124" s="32"/>
       <c r="C124" s="7"/>
@@ -2289,7 +2554,7 @@
       <c r="H124" s="8"/>
       <c r="I124" s="9"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="32"/>
       <c r="B125" s="32"/>
       <c r="C125" s="7"/>
@@ -2300,7 +2565,7 @@
       <c r="H125" s="8"/>
       <c r="I125" s="9"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="32"/>
       <c r="B126" s="32"/>
       <c r="C126" s="7"/>
@@ -2311,7 +2576,7 @@
       <c r="H126" s="8"/>
       <c r="I126" s="9"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="32"/>
       <c r="B127" s="32"/>
       <c r="C127" s="7"/>
@@ -2322,7 +2587,7 @@
       <c r="H127" s="8"/>
       <c r="I127" s="9"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="32"/>
       <c r="B128" s="32"/>
       <c r="C128" s="7"/>
@@ -2333,7 +2598,7 @@
       <c r="H128" s="8"/>
       <c r="I128" s="9"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="32"/>
       <c r="B129" s="32"/>
       <c r="C129" s="7"/>
@@ -2344,7 +2609,7 @@
       <c r="H129" s="8"/>
       <c r="I129" s="9"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="32"/>
       <c r="B130" s="32"/>
       <c r="C130" s="7"/>
@@ -2355,7 +2620,7 @@
       <c r="H130" s="8"/>
       <c r="I130" s="9"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="32"/>
       <c r="B131" s="32"/>
       <c r="C131" s="7"/>
@@ -2366,7 +2631,7 @@
       <c r="H131" s="8"/>
       <c r="I131" s="9"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="32"/>
       <c r="B132" s="32"/>
       <c r="C132" s="7"/>
@@ -2377,7 +2642,7 @@
       <c r="H132" s="8"/>
       <c r="I132" s="9"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="32"/>
       <c r="B133" s="32"/>
       <c r="C133" s="7"/>
@@ -2388,7 +2653,7 @@
       <c r="H133" s="8"/>
       <c r="I133" s="9"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="32"/>
       <c r="B134" s="32"/>
       <c r="C134" s="7"/>
@@ -2399,7 +2664,7 @@
       <c r="H134" s="8"/>
       <c r="I134" s="9"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="32"/>
       <c r="B135" s="32"/>
       <c r="C135" s="7"/>
@@ -2410,7 +2675,7 @@
       <c r="H135" s="8"/>
       <c r="I135" s="9"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="32"/>
       <c r="B136" s="32"/>
       <c r="C136" s="7"/>
@@ -2421,7 +2686,7 @@
       <c r="H136" s="8"/>
       <c r="I136" s="9"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="32"/>
       <c r="B137" s="32"/>
       <c r="C137" s="7"/>
@@ -2432,7 +2697,7 @@
       <c r="H137" s="8"/>
       <c r="I137" s="9"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="32"/>
       <c r="B138" s="32"/>
       <c r="C138" s="7"/>
@@ -2443,7 +2708,7 @@
       <c r="H138" s="8"/>
       <c r="I138" s="9"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="32"/>
       <c r="B139" s="32"/>
       <c r="C139" s="7"/>
@@ -2454,7 +2719,7 @@
       <c r="H139" s="8"/>
       <c r="I139" s="9"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="32"/>
       <c r="B140" s="32"/>
       <c r="C140" s="7"/>
@@ -2465,7 +2730,7 @@
       <c r="H140" s="8"/>
       <c r="I140" s="9"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="32"/>
       <c r="B141" s="32"/>
       <c r="C141" s="7"/>
@@ -2476,7 +2741,7 @@
       <c r="H141" s="8"/>
       <c r="I141" s="9"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="32"/>
       <c r="B142" s="32"/>
       <c r="C142" s="7"/>
@@ -2487,7 +2752,7 @@
       <c r="H142" s="8"/>
       <c r="I142" s="9"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="32"/>
       <c r="B143" s="32"/>
       <c r="C143" s="7"/>
@@ -2498,7 +2763,7 @@
       <c r="H143" s="8"/>
       <c r="I143" s="9"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="32"/>
       <c r="B144" s="32"/>
       <c r="C144" s="7"/>
@@ -2509,7 +2774,7 @@
       <c r="H144" s="8"/>
       <c r="I144" s="9"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="11"/>
       <c r="C145" s="11"/>
@@ -2520,7 +2785,7 @@
       <c r="H145" s="8"/>
       <c r="I145" s="9"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="11"/>
       <c r="C146" s="11"/>
@@ -2531,7 +2796,7 @@
       <c r="H146" s="8"/>
       <c r="I146" s="9"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="11"/>
       <c r="C147" s="11"/>
@@ -2542,7 +2807,7 @@
       <c r="H147" s="8"/>
       <c r="I147" s="9"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
       <c r="B148" s="11"/>
       <c r="C148" s="11"/>
@@ -2553,7 +2818,7 @@
       <c r="H148" s="8"/>
       <c r="I148" s="9"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="10"/>
       <c r="B149" s="11"/>
       <c r="C149" s="11"/>
@@ -2564,7 +2829,7 @@
       <c r="H149" s="8"/>
       <c r="I149" s="9"/>
     </row>
-    <row r="150" spans="1:9" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="150" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -2576,7 +2841,13 @@
       <c r="I150" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="15">
+    <mergeCell ref="A25:A43"/>
+    <mergeCell ref="B25:B43"/>
+    <mergeCell ref="C25:C43"/>
+    <mergeCell ref="C44:C52"/>
+    <mergeCell ref="A44:A52"/>
+    <mergeCell ref="B44:B52"/>
     <mergeCell ref="A12:A24"/>
     <mergeCell ref="C12:C24"/>
     <mergeCell ref="B4:B11"/>
@@ -2588,6 +2859,6 @@
     <mergeCell ref="D8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MidiPyGenStatus.xlsx
+++ b/MidiPyGenStatus.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="84">
   <si>
     <t>Date</t>
   </si>
@@ -253,6 +253,24 @@
   </si>
   <si>
     <t>Add Percussion</t>
+  </si>
+  <si>
+    <t>ERROR: QUINTET DOESN’T WORK! ENDS UP WITH DIATONIC OF 0 FOR EXTRA INSTRUMENT</t>
+  </si>
+  <si>
+    <t>Feature additions</t>
+  </si>
+  <si>
+    <t>In Work</t>
+  </si>
+  <si>
+    <t>Quintet error is fixed</t>
+  </si>
+  <si>
+    <t>Borrowed Chords and Seventh Chords</t>
+  </si>
+  <si>
+    <t>Melody generation using motif and periods</t>
   </si>
 </sst>
 </file>
@@ -572,7 +590,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -613,6 +631,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -652,8 +673,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1009,13 +1029,13 @@
       <c r="I3" s="21"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="45">
+      <c r="A4" s="48">
         <v>43095</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="49" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="23" t="s">
@@ -1028,9 +1048,9 @@
       <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="45"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="46"/>
+      <c r="A5" s="48"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="49"/>
       <c r="D5" s="26" t="s">
         <v>10</v>
       </c>
@@ -1043,14 +1063,14 @@
       <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="43" t="s">
+      <c r="A6" s="48"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
       <c r="G6" s="8" t="s">
         <v>15</v>
       </c>
@@ -1058,14 +1078,14 @@
       <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="45"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="43" t="s">
+      <c r="A7" s="48"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
       <c r="G7" s="8" t="s">
         <v>19</v>
       </c>
@@ -1073,14 +1093,14 @@
       <c r="I7" s="27"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="45"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="43" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
       <c r="G8" s="8" t="s">
         <v>20</v>
       </c>
@@ -1088,9 +1108,9 @@
       <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="46"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="26" t="s">
         <v>14</v>
       </c>
@@ -1101,9 +1121,9 @@
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="46"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="28" t="s">
         <v>16</v>
       </c>
@@ -1114,9 +1134,9 @@
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="45"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="46"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="29" t="s">
         <v>17</v>
       </c>
@@ -1127,13 +1147,13 @@
       <c r="I11" s="31"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="34">
+      <c r="A12" s="37">
         <v>43097</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="40" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="23" t="s">
@@ -1146,9 +1166,9 @@
       <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="35"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="38"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="26" t="s">
         <v>22</v>
       </c>
@@ -1161,9 +1181,9 @@
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="38"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="41"/>
       <c r="D14" s="28" t="s">
         <v>23</v>
       </c>
@@ -1176,9 +1196,9 @@
       <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="35"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="38"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="28" t="s">
         <v>30</v>
       </c>
@@ -1191,9 +1211,9 @@
       <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="35"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="38"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="28" t="s">
         <v>25</v>
       </c>
@@ -1204,9 +1224,9 @@
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
-      <c r="B17" s="41"/>
-      <c r="C17" s="38"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="28" t="s">
         <v>26</v>
       </c>
@@ -1217,9 +1237,9 @@
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="35"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="38"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="28" t="s">
         <v>29</v>
       </c>
@@ -1230,9 +1250,9 @@
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="35"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="38"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="28"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -1241,9 +1261,9 @@
       <c r="I19" s="27"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="35"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="38"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="26" t="s">
         <v>10</v>
       </c>
@@ -1256,9 +1276,9 @@
       <c r="I20" s="27"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="35"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="38"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="28" t="s">
         <v>31</v>
       </c>
@@ -1271,9 +1291,9 @@
       <c r="I21" s="27"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="35"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="38"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="28" t="s">
         <v>24</v>
       </c>
@@ -1286,9 +1306,9 @@
       <c r="I22" s="27"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="35"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="38"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="41"/>
       <c r="D23" s="1" t="s">
         <v>34</v>
       </c>
@@ -1301,9 +1321,9 @@
       <c r="I23" s="27"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="39"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="42"/>
       <c r="D24" s="29" t="s">
         <v>35</v>
       </c>
@@ -1316,13 +1336,13 @@
       <c r="I24" s="31"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="45">
+      <c r="A25" s="48">
         <v>43100</v>
       </c>
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="49" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="23" t="s">
@@ -1335,9 +1355,9 @@
       <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="46"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
       <c r="D26" s="26" t="s">
         <v>22</v>
       </c>
@@ -1350,9 +1370,9 @@
       <c r="I26" s="27"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="45"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="46"/>
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
       <c r="D27" s="28" t="s">
         <v>39</v>
       </c>
@@ -1365,9 +1385,9 @@
       <c r="I27" s="27"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="45"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="46"/>
+      <c r="A28" s="48"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49"/>
       <c r="D28" s="28" t="s">
         <v>40</v>
       </c>
@@ -1380,9 +1400,9 @@
       <c r="I28" s="27"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="45"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="46"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="26" t="s">
         <v>50</v>
       </c>
@@ -1395,9 +1415,9 @@
       <c r="I29" s="27"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="46"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49"/>
       <c r="D30" s="28" t="s">
         <v>51</v>
       </c>
@@ -1410,9 +1430,9 @@
       <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="45"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="46"/>
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="49"/>
       <c r="D31" s="28" t="s">
         <v>52</v>
       </c>
@@ -1425,9 +1445,9 @@
       <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="45"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="46"/>
+      <c r="A32" s="48"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="49"/>
       <c r="D32" s="28" t="s">
         <v>53</v>
       </c>
@@ -1442,9 +1462,9 @@
       <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="45"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="46"/>
+      <c r="A33" s="48"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="49"/>
       <c r="D33" s="28" t="s">
         <v>55</v>
       </c>
@@ -1457,9 +1477,9 @@
       <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="45"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="46"/>
+      <c r="A34" s="48"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="49"/>
       <c r="D34" s="28" t="s">
         <v>56</v>
       </c>
@@ -1472,9 +1492,9 @@
       <c r="I34" s="27"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="45"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="46"/>
+      <c r="A35" s="48"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="49"/>
       <c r="D35" s="28" t="s">
         <v>58</v>
       </c>
@@ -1487,9 +1507,9 @@
       <c r="I35" s="27"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="45"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="46"/>
+      <c r="A36" s="48"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="49"/>
       <c r="D36" s="28" t="s">
         <v>57</v>
       </c>
@@ -1504,9 +1524,9 @@
       <c r="I36" s="27"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="45"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="46"/>
+      <c r="A37" s="48"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="49"/>
       <c r="D37" s="28" t="s">
         <v>59</v>
       </c>
@@ -1526,9 +1546,9 @@
       <c r="I37" s="27"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="45"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="46"/>
+      <c r="A38" s="48"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="49"/>
       <c r="D38" s="28" t="s">
         <v>60</v>
       </c>
@@ -1545,9 +1565,9 @@
       <c r="I38" s="27"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="45"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="46"/>
+      <c r="A39" s="48"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="49"/>
       <c r="D39" s="28" t="s">
         <v>61</v>
       </c>
@@ -1564,9 +1584,9 @@
       <c r="I39" s="27"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="45"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="46"/>
+      <c r="A40" s="48"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="49"/>
       <c r="D40" s="28" t="s">
         <v>57</v>
       </c>
@@ -1581,9 +1601,9 @@
       <c r="I40" s="27"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="45"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="46"/>
+      <c r="A41" s="48"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="49"/>
       <c r="D41" s="28" t="s">
         <v>64</v>
       </c>
@@ -1600,9 +1620,9 @@
       <c r="I41" s="27"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="45"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="46"/>
+      <c r="A42" s="48"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="49"/>
       <c r="D42" s="28" t="s">
         <v>68</v>
       </c>
@@ -1619,9 +1639,9 @@
       <c r="I42" s="27"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="45"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="46"/>
+      <c r="A43" s="48"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="49"/>
       <c r="D43" s="29" t="s">
         <v>67</v>
       </c>
@@ -1638,19 +1658,19 @@
       <c r="I43" s="31"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="40">
+      <c r="A44" s="43">
         <v>43104</v>
       </c>
-      <c r="B44" s="40" t="s">
+      <c r="B44" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="37" t="s">
+      <c r="C44" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="47" t="s">
+      <c r="D44" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="35" t="s">
         <v>74</v>
       </c>
       <c r="F44" s="24"/>
@@ -1659,9 +1679,9 @@
       <c r="I44" s="25"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="41"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="38"/>
+      <c r="A45" s="44"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="41"/>
       <c r="D45" s="28" t="s">
         <v>69</v>
       </c>
@@ -1672,9 +1692,9 @@
       <c r="I45" s="27"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="41"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="38"/>
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="41"/>
       <c r="D46" s="28" t="s">
         <v>70</v>
       </c>
@@ -1685,9 +1705,9 @@
       <c r="I46" s="27"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="41"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="38"/>
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="41"/>
       <c r="D47" s="26" t="s">
         <v>71</v>
       </c>
@@ -1698,9 +1718,9 @@
       <c r="I47" s="27"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="41"/>
-      <c r="B48" s="41"/>
-      <c r="C48" s="38"/>
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="41"/>
       <c r="D48" s="28" t="s">
         <v>72</v>
       </c>
@@ -1711,9 +1731,9 @@
       <c r="I48" s="27"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="41"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="38"/>
+      <c r="A49" s="44"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="41"/>
       <c r="D49" s="28" t="s">
         <v>76</v>
       </c>
@@ -1724,9 +1744,9 @@
       <c r="I49" s="27"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="41"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="38"/>
+      <c r="A50" s="44"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="41"/>
       <c r="D50" s="28"/>
       <c r="E50" s="8" t="s">
         <v>75</v>
@@ -1737,9 +1757,9 @@
       <c r="I50" s="27"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="41"/>
-      <c r="B51" s="41"/>
-      <c r="C51" s="38"/>
+      <c r="A51" s="44"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="41"/>
       <c r="D51" s="28" t="s">
         <v>73</v>
       </c>
@@ -1750,67 +1770,86 @@
       <c r="I51" s="27"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="42"/>
-      <c r="B52" s="42"/>
-      <c r="C52" s="39"/>
+      <c r="A52" s="45"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="42"/>
       <c r="D52" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="E52" s="30"/>
+      <c r="E52" s="36" t="s">
+        <v>78</v>
+      </c>
       <c r="F52" s="30"/>
       <c r="G52" s="30"/>
       <c r="H52" s="30"/>
       <c r="I52" s="31"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="32"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="9"/>
+      <c r="A53" s="48">
+        <v>43107</v>
+      </c>
+      <c r="B53" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="H53" s="24"/>
+      <c r="I53" s="25"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="32"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+      <c r="A54" s="48"/>
+      <c r="B54" s="48"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="28" t="s">
+        <v>81</v>
+      </c>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
+      <c r="G54" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="H54" s="8"/>
-      <c r="I54" s="9"/>
+      <c r="I54" s="27"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="32"/>
-      <c r="B55" s="32"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
+      <c r="A55" s="48"/>
+      <c r="B55" s="48"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="26" t="s">
+        <v>79</v>
+      </c>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
-      <c r="I55" s="9"/>
+      <c r="I55" s="27"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="32"/>
-      <c r="B56" s="32"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="9"/>
+      <c r="A56" s="48"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="31"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="32"/>
       <c r="B57" s="32"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
@@ -2841,7 +2880,10 @@
       <c r="I150" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
+    <mergeCell ref="C53:C56"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="A53:A56"/>
     <mergeCell ref="A25:A43"/>
     <mergeCell ref="B25:B43"/>
     <mergeCell ref="C25:C43"/>
